--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FRCoreValueSetIdentityReliabilityStatus</t>
+    <t>FRCoreValueSetIdentityReliability</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The reliability of the identity.</t>
+    <t>Les 4 statuts de confiance de l'identité définis par le RNIV [EXI SI 07]. Ces statuts sont exclusifs les uns des autres.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0445</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-identity-reliability</t>
   </si>
 </sst>
 </file>

--- a/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
